--- a/releases/evt-pre-20/2026-09-30-rev-d/Основной_пакет/01_Закупка/BOM_EVT_PRE_20_оценочные_цены.xlsx
+++ b/releases/evt-pre-20/2026-09-30-rev-d/Основной_пакет/01_Закупка/BOM_EVT_PRE_20_оценочные_цены.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка закупки" sheetId="1" r:id="R61a15c257dc34089"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены v02" sheetId="2" r:id="R553626595a8841ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNP" sheetId="3" r:id="Rd67cbfa42ddd486b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка закупки" sheetId="1" r:id="R8e6dd74e9593466f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены v02" sheetId="2" r:id="R3ab9c235aaf14899"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNP" sheetId="3" r:id="Ra463d3fa6d5d4dcd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -671,7 +671,7 @@
         <x:v>DIO-ASM-PWR-REV-A</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>4-layer PCB-PWR Rev A PCBA; JLC04161H-3313A order basis; 90x60x1.6 mm; ENIG; outer 2 oz / 70 um, inner 1 oz / 35 um; fab DFM and actual stack ID at checkout</x:v>
+        <x:v>4-layer PCB-PWR Rev A PCBA; 90x60x1.6 mm; ENIG; 1 oz / 35 um copper on all four layers; fabricator stack ID and DFM at checkout</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
         <x:v>N/A</x:v>
@@ -6230,7 +6230,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bb7934a927f4d12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1b022b46e084a09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7928,7 +7928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d63aadd1ce04921"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5aa7df70de6430e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8148,7 +8148,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52e1f29af00242bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re380c74ea45542af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/releases/evt-pre-20/2026-09-30-rev-d/Основной_пакет/01_Закупка/BOM_EVT_PRE_20_оценочные_цены.xlsx
+++ b/releases/evt-pre-20/2026-09-30-rev-d/Основной_пакет/01_Закупка/BOM_EVT_PRE_20_оценочные_цены.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка закупки" sheetId="1" r:id="R8e6dd74e9593466f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены v02" sheetId="2" r:id="R3ab9c235aaf14899"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNP" sheetId="3" r:id="Ra463d3fa6d5d4dcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка закупки" sheetId="1" r:id="Rc82ea9871265493f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены v02" sheetId="2" r:id="R8c74d1bfb28e4b7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNP" sheetId="3" r:id="R9890e5560234467f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -464,7 +464,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="3" t="str">
-        <x:v>Rev D: PCB-MAIN полностью разведен (DRC/unconnected/ERC 0/0/0); PCB-MIC Review B принят; PCB-PWR и PCB-MAIN передаются с обязательным DFM и подтверждением фактического стека.</x:v>
+        <x:v>Rev D: платы MAIN 22, PWR 22 и MIC 80 заказываются и изготавливаются полными партиями без паузы; DFM и фактический стек подтверждаются до запуска панели.</x:v>
       </x:c>
       <x:c r="B5" s="3"/>
       <x:c r="C5" s="3"/>
@@ -484,6 +484,11 @@
       <x:c r="Q5" s="3"/>
       <x:c r="R5" s="3"/>
     </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Энергосистема в сводке: аккумулятор RB40 - PR-097, MPPT - PR-099, солнечная панель SLP080S-12M - PR-101; количества первого лота 21/21/21 с резервом.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="7" ht="34" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>ID</x:v>
@@ -617,7 +622,7 @@
         <x:v>DIO-ASM-MIC-REV-B</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>2-layer PCB-MIC Rev B PCBA; 24x22x1.0 mm; ENIG; controlled acoustic port and first article</x:v>
+        <x:v>2-layer PCB-MIC Rev B PCBA; 24x22x1.0 mm; ENIG; full lot 80 no pause; post-lot acoustic sample</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
         <x:v>N/A</x:v>
@@ -645,7 +650,7 @@
         <x:v>HISTORICAL_ANALOG_NOT_QUOTE</x:v>
       </x:c>
       <x:c r="R9" s="11" t="str">
-        <x:v>REVIEW_B_ACCEPT_CONTROLLED_FIRST_ARTICLE</x:v>
+        <x:v>REVIEW_B_DESIGN_ACCEPT_CUSTOMER_FULL_LOT_NO_PAUSE</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -6227,10 +6232,11 @@
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A5:R5"/>
+    <x:mergeCell ref="A6:R6"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1b022b46e084a09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7506f74d624a47a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7928,7 +7934,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5aa7df70de6430e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9653dfe432614e88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8148,7 +8154,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re380c74ea45542af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47838db088964cbf"/>
   </x:tableParts>
 </x:worksheet>
 </file>